--- a/DateBase/orders/Nhat 48_2026-10-5.xlsx
+++ b/DateBase/orders/Nhat 48_2026-10-5.xlsx
@@ -641,6 +641,9 @@
       <c r="G2" t="str">
         <v>010520973055152510101072606520</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
